--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8236,0.0081,0.0142,0.1872</t>
-  </si>
-  <si>
-    <t>0.0132,0.0021,0.0025,0.9938</t>
-  </si>
-  <si>
-    <t>0.7180,0.0144,0.0133,0.3307</t>
-  </si>
-  <si>
-    <t>0.3341,0.0053,0.0031,0.8392</t>
-  </si>
-  <si>
-    <t>0.9871,0.0106,0.0025,0.0015</t>
-  </si>
-  <si>
-    <t>0.9807,0.0104,0.0047,0.0040</t>
-  </si>
-  <si>
-    <t>0.9845,0.0087,0.0013,0.0029</t>
-  </si>
-  <si>
-    <t>0.9804,0.0167,0.0039,0.0024</t>
-  </si>
-  <si>
-    <t>0.9441,0.0936,0.0098,0.0029</t>
-  </si>
-  <si>
-    <t>0.9694,0.0421,0.0076,0.0020</t>
-  </si>
-  <si>
-    <t>0.9891,0.0074,0.0017,0.0015</t>
-  </si>
-  <si>
-    <t>0.9677,0.0121,0.0164,0.0061</t>
-  </si>
-  <si>
-    <t>0.8498,0.0352,0.0829,0.0118</t>
-  </si>
-  <si>
-    <t>0.4338,0.0243,0.6867,0.0029</t>
-  </si>
-  <si>
-    <t>0.4552,0.0201,0.6797,0.0036</t>
-  </si>
-  <si>
-    <t>0.0398,0.0125,0.9576,0.0018</t>
-  </si>
-  <si>
-    <t>0.7889,0.0693,0.1405,0.0075</t>
-  </si>
-  <si>
-    <t>0.0028,0.9924,0.0116,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.9909,0.0083,0.0019</t>
-  </si>
-  <si>
-    <t>0.0226,0.9610,0.0243,0.0040</t>
-  </si>
-  <si>
-    <t>0.0062,0.9888,0.0047,0.0027</t>
-  </si>
-  <si>
-    <t>0.0011,0.9935,0.0240,0.0004</t>
-  </si>
-  <si>
-    <t>0.7063,0.0272,0.2350,0.0455</t>
-  </si>
-  <si>
-    <t>0.2661,0.0157,0.7090,0.0224</t>
-  </si>
-  <si>
-    <t>0.0123,0.0007,0.9620,0.0090</t>
-  </si>
-  <si>
-    <t>0.0964,0.0061,0.8961,0.0045</t>
-  </si>
-  <si>
-    <t>0.0060,0.0027,0.9783,0.0099</t>
-  </si>
-  <si>
-    <t>0.0239,0.0026,0.9450,0.0133</t>
-  </si>
-  <si>
-    <t>0.0014,0.0016,0.9942,0.0026</t>
-  </si>
-  <si>
-    <t>0.2621,0.6604,0.0611,0.0078</t>
-  </si>
-  <si>
-    <t>0.8135,0.1083,0.0655,0.0068</t>
-  </si>
-  <si>
-    <t>0.0002,0.0036,0.9986,0.0010</t>
-  </si>
-  <si>
-    <t>0.0164,0.9313,0.0807,0.0022</t>
-  </si>
-  <si>
-    <t>0.6327,0.3200,0.0449,0.0297</t>
-  </si>
-  <si>
-    <t>0.7640,0.1282,0.1240,0.0187</t>
-  </si>
-  <si>
-    <t>0.5154,0.5637,0.0347,0.0034</t>
-  </si>
-  <si>
-    <t>0.0499,0.8820,0.1779,0.0038</t>
-  </si>
-  <si>
-    <t>0.0052,0.6940,0.2318,0.1334</t>
-  </si>
-  <si>
-    <t>0.0067,0.0077,0.9236,0.1231</t>
-  </si>
-  <si>
-    <t>0.0053,0.0393,0.9648,0.0097</t>
-  </si>
-  <si>
-    <t>0.0295,0.0023,0.8530,0.0735</t>
-  </si>
-  <si>
-    <t>0.0128,0.0683,0.9113,0.0128</t>
-  </si>
-  <si>
-    <t>0.0001,0.9988,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.0067,0.0117,0.9771,0.0077</t>
-  </si>
-  <si>
-    <t>0.0210,0.6190,0.0115,0.7869</t>
-  </si>
-  <si>
-    <t>0.0085,0.9725,0.0145,0.0158</t>
-  </si>
-  <si>
-    <t>0.0004,0.9928,0.1049,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9948,0.0196,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0017,0.9944,0.0110</t>
-  </si>
-  <si>
-    <t>0.0024,0.4645,0.9558,0.0019</t>
-  </si>
-  <si>
-    <t>0.0024,0.0024,0.9849,0.0121</t>
-  </si>
-  <si>
-    <t>0.0050,0.0024,0.9837,0.0042</t>
-  </si>
-  <si>
-    <t>0.0015,0.0015,0.9940,0.0017</t>
-  </si>
-  <si>
-    <t>0.0015,0.0044,0.9874,0.0081</t>
-  </si>
-  <si>
-    <t>0.9280,0.0931,0.0197,0.0037</t>
-  </si>
-  <si>
-    <t>0.9656,0.0107,0.0278,0.0007</t>
-  </si>
-  <si>
-    <t>0.9195,0.0942,0.0243,0.0022</t>
-  </si>
-  <si>
-    <t>0.0010,0.0678,0.9970,0.0003</t>
-  </si>
-  <si>
-    <t>0.9787,0.0080,0.0063,0.0045</t>
-  </si>
-  <si>
-    <t>0.9787,0.0122,0.0088,0.0022</t>
-  </si>
-  <si>
-    <t>0.9769,0.0263,0.0050,0.0017</t>
-  </si>
-  <si>
-    <t>0.0006,0.8899,0.9380,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9953,0.0108</t>
-  </si>
-  <si>
-    <t>0.0026,0.0036,0.9828,0.0104</t>
-  </si>
-  <si>
-    <t>0.0004,0.9625,0.9421,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9984,0.0021</t>
-  </si>
-  <si>
-    <t>0.0064,0.9789,0.0300,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.9981,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.7107,0.0655,0.3404,0.0149</t>
-  </si>
-  <si>
-    <t>0.6007,0.2654,0.1733,0.0294</t>
-  </si>
-  <si>
-    <t>0.0054,0.0600,0.9708,0.0050</t>
-  </si>
-  <si>
-    <t>0.0016,0.8839,0.6144,0.0041</t>
-  </si>
-  <si>
-    <t>0.0005,0.9848,0.3096,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.9920,0.0132,0.0012</t>
-  </si>
-  <si>
-    <t>0.0008,0.9675,0.2079,0.0043</t>
-  </si>
-  <si>
-    <t>0.0230,0.0018,0.0078,0.9862</t>
-  </si>
-  <si>
-    <t>0.0056,0.0018,0.0017,0.9968</t>
-  </si>
-  <si>
-    <t>0.0038,0.0065,0.0006,0.9973</t>
-  </si>
-  <si>
-    <t>0.0154,0.0072,0.0095,0.9871</t>
-  </si>
-  <si>
-    <t>0.0395,0.0044,0.0122,0.9769</t>
-  </si>
-  <si>
-    <t>0.0147,0.0016,0.0033,0.9927</t>
-  </si>
-  <si>
-    <t>0.0004,0.9779,0.6903,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.8921,0.9747,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.7246,0.3979,0.0133</t>
-  </si>
-  <si>
-    <t>0.0052,0.3236,0.8281,0.0195</t>
-  </si>
-  <si>
-    <t>0.0003,0.9932,0.0552,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9559,0.4136,0.0023</t>
-  </si>
-  <si>
-    <t>0.9869,0.0069,0.0013,0.0024</t>
-  </si>
-  <si>
-    <t>0.8967,0.0918,0.0433,0.0044</t>
-  </si>
-  <si>
-    <t>0.9611,0.0428,0.0122,0.0017</t>
-  </si>
-  <si>
-    <t>0.9623,0.0335,0.0149,0.0030</t>
-  </si>
-  <si>
-    <t>0.9537,0.0629,0.0117,0.0026</t>
-  </si>
-  <si>
-    <t>0.9709,0.0299,0.0096,0.0025</t>
-  </si>
-  <si>
-    <t>0.9504,0.0683,0.0134,0.0029</t>
-  </si>
-  <si>
-    <t>0.9747,0.0152,0.0115,0.0020</t>
-  </si>
-  <si>
-    <t>0.9843,0.0091,0.0051,0.0020</t>
-  </si>
-  <si>
-    <t>0.9866,0.0088,0.0057,0.0008</t>
-  </si>
-  <si>
-    <t>0.9769,0.0205,0.0028,0.0036</t>
-  </si>
-  <si>
-    <t>0.9894,0.0062,0.0022,0.0016</t>
-  </si>
-  <si>
-    <t>0.9877,0.0103,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9502,0.0426,0.0233,0.0048</t>
-  </si>
-  <si>
-    <t>0.9726,0.0158,0.0108,0.0032</t>
-  </si>
-  <si>
-    <t>0.9901,0.0047,0.0023,0.0017</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9979,0.0024</t>
-  </si>
-  <si>
-    <t>0.0052,0.0063,0.9837,0.0039</t>
-  </si>
-  <si>
-    <t>0.8441,0.0084,0.2054,0.0050</t>
-  </si>
-  <si>
-    <t>0.0036,0.0020,0.9876,0.0046</t>
-  </si>
-  <si>
-    <t>0.0243,0.9666,0.0149,0.0039</t>
-  </si>
-  <si>
-    <t>0.0061,0.9807,0.0528,0.0015</t>
-  </si>
-  <si>
-    <t>0.0126,0.9809,0.0088,0.0052</t>
-  </si>
-  <si>
-    <t>0.0292,0.8645,0.2346,0.0028</t>
-  </si>
-  <si>
-    <t>0.0094,0.9720,0.0537,0.0011</t>
-  </si>
-  <si>
-    <t>0.0082,0.9822,0.0202,0.0028</t>
-  </si>
-  <si>
-    <t>0.7324,0.2791,0.0276,0.0019</t>
-  </si>
-  <si>
-    <t>0.5100,0.1205,0.4751,0.0179</t>
-  </si>
-  <si>
-    <t>0.1622,0.0080,0.8771,0.0026</t>
-  </si>
-  <si>
-    <t>0.5212,0.0274,0.5203,0.0087</t>
-  </si>
-  <si>
-    <t>0.5784,0.1021,0.3465,0.0510</t>
-  </si>
-  <si>
-    <t>0.1483,0.2334,0.0965,0.6765</t>
-  </si>
-  <si>
-    <t>0.0005,0.9954,0.0326,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0070,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.9945,0.0059,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.9948,0.3912,0.0004</t>
-  </si>
-  <si>
-    <t>0.0042,0.9715,0.1739,0.0002</t>
-  </si>
-  <si>
-    <t>0.7994,0.1223,0.0778,0.0017</t>
-  </si>
-  <si>
-    <t>0.7294,0.2021,0.0982,0.0061</t>
-  </si>
-  <si>
-    <t>0.9426,0.0316,0.0168,0.0145</t>
-  </si>
-  <si>
-    <t>0.9799,0.0086,0.0071,0.0035</t>
-  </si>
-  <si>
-    <t>0.9343,0.0653,0.0201,0.0064</t>
-  </si>
-  <si>
-    <t>0.9816,0.0075,0.0052,0.0049</t>
-  </si>
-  <si>
-    <t>0.9870,0.0027,0.0017,0.0063</t>
-  </si>
-  <si>
-    <t>0.9814,0.0102,0.0083,0.0028</t>
-  </si>
-  <si>
-    <t>0.9683,0.0113,0.0039,0.0105</t>
-  </si>
-  <si>
-    <t>0.9634,0.0113,0.0064,0.0152</t>
-  </si>
-  <si>
-    <t>0.0036,0.5080,0.8609,0.0034</t>
-  </si>
-  <si>
-    <t>0.0130,0.3736,0.7062,0.0222</t>
-  </si>
-  <si>
-    <t>0.0025,0.0363,0.9600,0.0029</t>
-  </si>
-  <si>
-    <t>0.0171,0.0586,0.9088,0.0151</t>
-  </si>
-  <si>
-    <t>0.5897,0.1329,0.1446,0.1780</t>
-  </si>
-  <si>
-    <t>0.7293,0.0317,0.2916,0.0048</t>
-  </si>
-  <si>
-    <t>0.6732,0.0179,0.4911,0.0042</t>
-  </si>
-  <si>
-    <t>0.7378,0.0453,0.2562,0.0068</t>
-  </si>
-  <si>
-    <t>0.0590,0.0011,0.0079,0.9710</t>
-  </si>
-  <si>
-    <t>0.0012,0.0005,0.0009,0.9990</t>
-  </si>
-  <si>
-    <t>0.0049,0.0046,0.0045,0.9953</t>
-  </si>
-  <si>
-    <t>0.0120,0.0005,0.0031,0.9940</t>
-  </si>
-  <si>
-    <t>0.0002,0.9860,0.1308,0.0038</t>
-  </si>
-  <si>
-    <t>0.9770,0.0194,0.0053,0.0024</t>
-  </si>
-  <si>
-    <t>0.1406,0.8137,0.0471,0.0112</t>
-  </si>
-  <si>
-    <t>0.9753,0.0154,0.0060,0.0035</t>
-  </si>
-  <si>
-    <t>0.7201,0.1651,0.0863,0.0027</t>
-  </si>
-  <si>
-    <t>0.9804,0.0036,0.0028,0.0073</t>
-  </si>
-  <si>
-    <t>0.8720,0.0320,0.0327,0.0583</t>
-  </si>
-  <si>
-    <t>0.9762,0.0178,0.0096,0.0022</t>
-  </si>
-  <si>
-    <t>0.0037,0.0853,0.9330,0.0777</t>
-  </si>
-  <si>
-    <t>0.8999,0.0062,0.0119,0.0723</t>
-  </si>
-  <si>
-    <t>0.8929,0.0448,0.0254,0.0282</t>
-  </si>
-  <si>
-    <t>0.1603,0.8307,0.0431,0.0068</t>
-  </si>
-  <si>
-    <t>0.8864,0.0690,0.0442,0.0055</t>
-  </si>
-  <si>
-    <t>0.8033,0.1353,0.0746,0.0068</t>
-  </si>
-  <si>
-    <t>0.1111,0.7869,0.1284,0.0693</t>
-  </si>
-  <si>
-    <t>0.3651,0.1719,0.5876,0.0266</t>
-  </si>
-  <si>
-    <t>0.6662,0.1966,0.1470,0.0203</t>
-  </si>
-  <si>
-    <t>0.9756,0.0168,0.0096,0.0022</t>
-  </si>
-  <si>
-    <t>0.9784,0.0065,0.0039,0.0081</t>
-  </si>
-  <si>
-    <t>0.9816,0.0077,0.0058,0.0031</t>
-  </si>
-  <si>
-    <t>0.9638,0.0204,0.0052,0.0076</t>
-  </si>
-  <si>
-    <t>0.9826,0.0051,0.0041,0.0055</t>
-  </si>
-  <si>
-    <t>0.9709,0.0171,0.0160,0.0013</t>
-  </si>
-  <si>
-    <t>0.9890,0.0035,0.0032,0.0020</t>
-  </si>
-  <si>
-    <t>0.9866,0.0061,0.0013,0.0028</t>
-  </si>
-  <si>
-    <t>0.3685,0.4239,0.2310,0.0059</t>
-  </si>
-  <si>
-    <t>0.1496,0.7723,0.0638,0.0015</t>
-  </si>
-  <si>
-    <t>0.4134,0.6716,0.0273,0.0057</t>
-  </si>
-  <si>
-    <t>0.7449,0.2126,0.0915,0.0141</t>
-  </si>
-  <si>
-    <t>0.9603,0.0627,0.0058,0.0018</t>
-  </si>
-  <si>
-    <t>0.9287,0.0597,0.0273,0.0133</t>
-  </si>
-  <si>
-    <t>0.9269,0.0428,0.0413,0.0010</t>
-  </si>
-  <si>
-    <t>0.9020,0.0921,0.0318,0.0106</t>
-  </si>
-  <si>
-    <t>0.0001,0.0118,0.9990,0.0009</t>
-  </si>
-  <si>
-    <t>0.9783,0.0152,0.0100,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9950,0.0024</t>
-  </si>
-  <si>
-    <t>0.0043,0.0114,0.9761,0.0164</t>
-  </si>
-  <si>
-    <t>0.0515,0.0108,0.9407,0.0040</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9996,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9955,0.0041</t>
-  </si>
-  <si>
-    <t>0.0023,0.0021,0.9902,0.0043</t>
-  </si>
-  <si>
-    <t>0.0035,0.0018,0.9871,0.0064</t>
-  </si>
-  <si>
-    <t>0.4287,0.0101,0.7366,0.0017</t>
-  </si>
-  <si>
-    <t>0.1092,0.0103,0.8767,0.0090</t>
-  </si>
-  <si>
-    <t>0.1892,0.0556,0.8001,0.0066</t>
-  </si>
-  <si>
-    <t>0.0970,0.2403,0.6000,0.0057</t>
-  </si>
-  <si>
-    <t>0.1049,0.2416,0.7538,0.0093</t>
-  </si>
-  <si>
-    <t>0.3697,0.0268,0.6769,0.0023</t>
-  </si>
-  <si>
-    <t>0.5315,0.0169,0.5695,0.0051</t>
-  </si>
-  <si>
-    <t>0.2566,0.0723,0.7395,0.0077</t>
-  </si>
-  <si>
-    <t>0.4924,0.4960,0.0428,0.0020</t>
-  </si>
-  <si>
-    <t>0.4168,0.6104,0.0316,0.0020</t>
-  </si>
-  <si>
-    <t>0.9081,0.1397,0.0125,0.0018</t>
-  </si>
-  <si>
-    <t>0.8153,0.2481,0.0206,0.0027</t>
-  </si>
-  <si>
-    <t>0.4857,0.6047,0.0258,0.0064</t>
-  </si>
-  <si>
-    <t>0.7949,0.0310,0.1996,0.0113</t>
-  </si>
-  <si>
-    <t>0.7607,0.0195,0.1465,0.0376</t>
-  </si>
-  <si>
-    <t>0.6520,0.0273,0.0739,0.2141</t>
-  </si>
-  <si>
-    <t>0.5529,0.0138,0.5620,0.0062</t>
-  </si>
-  <si>
-    <t>0.6997,0.1434,0.1407,0.0171</t>
-  </si>
-  <si>
-    <t>0.0019,0.0033,0.9750,0.0562</t>
-  </si>
-  <si>
-    <t>0.0109,0.0071,0.8900,0.1105</t>
-  </si>
-  <si>
-    <t>0.0021,0.0216,0.9820,0.0108</t>
-  </si>
-  <si>
-    <t>0.0430,0.0112,0.8746,0.0318</t>
-  </si>
-  <si>
-    <t>0.0023,0.0120,0.9616,0.0328</t>
-  </si>
-  <si>
-    <t>0.9719,0.0156,0.0103,0.0047</t>
-  </si>
-  <si>
-    <t>0.9739,0.0244,0.0085,0.0017</t>
-  </si>
-  <si>
-    <t>0.9829,0.0105,0.0065,0.0018</t>
-  </si>
-  <si>
-    <t>0.9569,0.0263,0.0236,0.0019</t>
-  </si>
-  <si>
-    <t>0.9501,0.0480,0.0194,0.0041</t>
-  </si>
-  <si>
-    <t>0.9799,0.0173,0.0081,0.0009</t>
-  </si>
-  <si>
-    <t>0.9695,0.0297,0.0110,0.0024</t>
-  </si>
-  <si>
-    <t>0.9855,0.0117,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.0226,0.0225,0.9762,0.0028</t>
-  </si>
-  <si>
-    <t>0.3266,0.2298,0.4986,0.0100</t>
-  </si>
-  <si>
-    <t>0.7830,0.0372,0.1779,0.0341</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9917,0.0093</t>
-  </si>
-  <si>
-    <t>0.0003,0.0073,0.9944,0.0028</t>
-  </si>
-  <si>
-    <t>0.0127,0.0338,0.9279,0.0144</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9963,0.0055</t>
-  </si>
-  <si>
-    <t>0.0094,0.4966,0.7076,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9991,0.0028</t>
-  </si>
-  <si>
-    <t>0.0024,0.0023,0.9852,0.0059</t>
-  </si>
-  <si>
-    <t>0.0314,0.0322,0.9259,0.0104</t>
-  </si>
-  <si>
-    <t>0.8207,0.0242,0.1544,0.0202</t>
-  </si>
-  <si>
-    <t>0.8562,0.0167,0.1634,0.0044</t>
-  </si>
-  <si>
-    <t>0.8139,0.0157,0.1069,0.0371</t>
-  </si>
-  <si>
-    <t>0.9377,0.0655,0.0232,0.0070</t>
-  </si>
-  <si>
-    <t>0.9844,0.0142,0.0051,0.0014</t>
-  </si>
-  <si>
-    <t>0.9816,0.0140,0.0047,0.0027</t>
-  </si>
-  <si>
-    <t>0.9740,0.0225,0.0091,0.0022</t>
-  </si>
-  <si>
-    <t>0.9563,0.0225,0.0178,0.0086</t>
-  </si>
-  <si>
-    <t>0.9588,0.0255,0.0219,0.0019</t>
-  </si>
-  <si>
-    <t>0.9497,0.0411,0.0280,0.0049</t>
-  </si>
-  <si>
-    <t>0.9784,0.0121,0.0065,0.0037</t>
-  </si>
-  <si>
-    <t>0.0066,0.0040,0.9779,0.0040</t>
-  </si>
-  <si>
-    <t>0.0003,0.0027,0.9974,0.0007</t>
-  </si>
-  <si>
-    <t>0.0015,0.0476,0.9810,0.0051</t>
-  </si>
-  <si>
-    <t>0.0151,0.0315,0.9269,0.0197</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9942,0.0067</t>
-  </si>
-  <si>
-    <t>0.0944,0.0088,0.5561,0.2981</t>
-  </si>
-  <si>
-    <t>0.1119,0.0999,0.8291,0.0276</t>
-  </si>
-  <si>
-    <t>0.0325,0.0059,0.8773,0.0665</t>
-  </si>
-  <si>
-    <t>0.9208,0.0132,0.0198,0.0326</t>
-  </si>
-  <si>
-    <t>0.0282,0.0176,0.0067,0.9810</t>
-  </si>
-  <si>
-    <t>0.1409,0.0042,0.0055,0.9525</t>
-  </si>
-  <si>
-    <t>0.0069,0.0003,0.0007,0.9976</t>
-  </si>
-  <si>
-    <t>0.0069,0.0005,0.0051,0.9949</t>
-  </si>
-  <si>
-    <t>0.6647,0.0577,0.0304,0.2058</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8252,0.0583,0.1091,0.0494</t>
+  </si>
+  <si>
+    <t>0.0298,0.0023,0.0022,0.9891</t>
+  </si>
+  <si>
+    <t>0.8929,0.0040,0.0042,0.1287</t>
+  </si>
+  <si>
+    <t>0.3482,0.0045,0.0063,0.8164</t>
+  </si>
+  <si>
+    <t>0.9899,0.0051,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.9657,0.0429,0.0047,0.0029</t>
+  </si>
+  <si>
+    <t>0.9848,0.0104,0.0043,0.0022</t>
+  </si>
+  <si>
+    <t>0.9867,0.0087,0.0033,0.0019</t>
+  </si>
+  <si>
+    <t>0.9746,0.0274,0.0053,0.0028</t>
+  </si>
+  <si>
+    <t>0.9763,0.0181,0.0081,0.0028</t>
+  </si>
+  <si>
+    <t>0.9823,0.0165,0.0051,0.0012</t>
+  </si>
+  <si>
+    <t>0.9850,0.0071,0.0030,0.0033</t>
+  </si>
+  <si>
+    <t>0.8335,0.0240,0.1543,0.0044</t>
+  </si>
+  <si>
+    <t>0.0573,0.2422,0.8853,0.0050</t>
+  </si>
+  <si>
+    <t>0.6811,0.0399,0.3297,0.0041</t>
+  </si>
+  <si>
+    <t>0.1683,0.0179,0.8198,0.0090</t>
+  </si>
+  <si>
+    <t>0.8265,0.0163,0.2305,0.0074</t>
+  </si>
+  <si>
+    <t>0.0017,0.9958,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.9856,0.0178,0.0011</t>
+  </si>
+  <si>
+    <t>0.0861,0.9015,0.0301,0.0052</t>
+  </si>
+  <si>
+    <t>0.0128,0.9781,0.0081,0.0017</t>
+  </si>
+  <si>
+    <t>0.0014,0.9960,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.4574,0.0367,0.5607,0.0234</t>
+  </si>
+  <si>
+    <t>0.1232,0.0157,0.7019,0.0946</t>
+  </si>
+  <si>
+    <t>0.0556,0.0021,0.8716,0.0204</t>
+  </si>
+  <si>
+    <t>0.0193,0.0224,0.9498,0.0045</t>
+  </si>
+  <si>
+    <t>0.0063,0.0009,0.9893,0.0017</t>
+  </si>
+  <si>
+    <t>0.0335,0.0076,0.9496,0.0081</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.9884,0.0120</t>
+  </si>
+  <si>
+    <t>0.4396,0.3859,0.1044,0.0045</t>
+  </si>
+  <si>
+    <t>0.8096,0.0686,0.1610,0.0148</t>
+  </si>
+  <si>
+    <t>0.0014,0.0123,0.9936,0.0058</t>
+  </si>
+  <si>
+    <t>0.0037,0.9626,0.1772,0.0007</t>
+  </si>
+  <si>
+    <t>0.7913,0.1449,0.0732,0.0143</t>
+  </si>
+  <si>
+    <t>0.5283,0.1563,0.3201,0.0066</t>
+  </si>
+  <si>
+    <t>0.7920,0.2431,0.0266,0.0027</t>
+  </si>
+  <si>
+    <t>0.0562,0.8365,0.2307,0.0031</t>
+  </si>
+  <si>
+    <t>0.0061,0.2206,0.5856,0.1531</t>
+  </si>
+  <si>
+    <t>0.0026,0.0053,0.9802,0.0215</t>
+  </si>
+  <si>
+    <t>0.0078,0.0628,0.9391,0.0351</t>
+  </si>
+  <si>
+    <t>0.0398,0.0048,0.8538,0.0621</t>
+  </si>
+  <si>
+    <t>0.0303,0.0679,0.8926,0.0100</t>
+  </si>
+  <si>
+    <t>0.0002,0.9974,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.0142,0.0708,0.9109,0.0337</t>
+  </si>
+  <si>
+    <t>0.1106,0.3157,0.0097,0.6977</t>
+  </si>
+  <si>
+    <t>0.0004,0.9946,0.0083,0.0063</t>
+  </si>
+  <si>
+    <t>0.0002,0.9948,0.0173,0.0019</t>
+  </si>
+  <si>
+    <t>0.0007,0.9914,0.0961,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0229,0.9900,0.0080</t>
+  </si>
+  <si>
+    <t>0.0028,0.0852,0.9739,0.0053</t>
+  </si>
+  <si>
+    <t>0.0011,0.0013,0.9911,0.0071</t>
+  </si>
+  <si>
+    <t>0.0061,0.0023,0.9785,0.0114</t>
+  </si>
+  <si>
+    <t>0.0005,0.0021,0.9961,0.0030</t>
+  </si>
+  <si>
+    <t>0.0152,0.0298,0.9575,0.0091</t>
+  </si>
+  <si>
+    <t>0.8065,0.1866,0.0411,0.0037</t>
+  </si>
+  <si>
+    <t>0.9805,0.0044,0.0123,0.0019</t>
+  </si>
+  <si>
+    <t>0.9902,0.0069,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.0072,0.1903,0.9858,0.0022</t>
+  </si>
+  <si>
+    <t>0.9824,0.0082,0.0079,0.0015</t>
+  </si>
+  <si>
+    <t>0.9866,0.0067,0.0041,0.0018</t>
+  </si>
+  <si>
+    <t>0.9848,0.0128,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.8254,0.7370,0.0067</t>
+  </si>
+  <si>
+    <t>0.0001,0.0037,0.9979,0.0043</t>
+  </si>
+  <si>
+    <t>0.0011,0.0057,0.9845,0.0250</t>
+  </si>
+  <si>
+    <t>0.0010,0.9496,0.9237,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9991,0.0022</t>
+  </si>
+  <si>
+    <t>0.0097,0.9752,0.0149,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7373,0.0521,0.3176,0.0069</t>
+  </si>
+  <si>
+    <t>0.3535,0.1705,0.6348,0.0217</t>
+  </si>
+  <si>
+    <t>0.0012,0.0066,0.9948,0.0039</t>
+  </si>
+  <si>
+    <t>0.0041,0.7339,0.7950,0.0029</t>
+  </si>
+  <si>
+    <t>0.0046,0.8419,0.6534,0.0029</t>
+  </si>
+  <si>
+    <t>0.0003,0.9893,0.0439,0.0024</t>
+  </si>
+  <si>
+    <t>0.0002,0.9830,0.4181,0.0013</t>
+  </si>
+  <si>
+    <t>0.0498,0.0025,0.0200,0.9645</t>
+  </si>
+  <si>
+    <t>0.0031,0.0033,0.0060,0.9960</t>
+  </si>
+  <si>
+    <t>0.0025,0.0022,0.0010,0.9980</t>
+  </si>
+  <si>
+    <t>0.0386,0.0075,0.0057,0.9810</t>
+  </si>
+  <si>
+    <t>0.0749,0.0009,0.0025,0.9772</t>
+  </si>
+  <si>
+    <t>0.0084,0.0016,0.0020,0.9955</t>
+  </si>
+  <si>
+    <t>0.0009,0.9633,0.6718,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.9168,0.7373,0.0037</t>
+  </si>
+  <si>
+    <t>0.0013,0.9448,0.2132,0.0034</t>
+  </si>
+  <si>
+    <t>0.0026,0.2700,0.9703,0.0019</t>
+  </si>
+  <si>
+    <t>0.0004,0.9894,0.1141,0.0003</t>
+  </si>
+  <si>
+    <t>0.0037,0.8512,0.6805,0.0024</t>
+  </si>
+  <si>
+    <t>0.9899,0.0047,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.9782,0.0165,0.0099,0.0017</t>
+  </si>
+  <si>
+    <t>0.9790,0.0161,0.0067,0.0021</t>
+  </si>
+  <si>
+    <t>0.9376,0.0692,0.0221,0.0051</t>
+  </si>
+  <si>
+    <t>0.9239,0.0861,0.0229,0.0059</t>
+  </si>
+  <si>
+    <t>0.9778,0.0200,0.0071,0.0027</t>
+  </si>
+  <si>
+    <t>0.9716,0.0165,0.0131,0.0036</t>
+  </si>
+  <si>
+    <t>0.9671,0.0450,0.0076,0.0023</t>
+  </si>
+  <si>
+    <t>0.9858,0.0149,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.9866,0.0077,0.0052,0.0014</t>
+  </si>
+  <si>
+    <t>0.9795,0.0197,0.0027,0.0032</t>
+  </si>
+  <si>
+    <t>0.9918,0.0036,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.9824,0.0203,0.0037,0.0013</t>
+  </si>
+  <si>
+    <t>0.9776,0.0211,0.0059,0.0026</t>
+  </si>
+  <si>
+    <t>0.9849,0.0069,0.0026,0.0034</t>
+  </si>
+  <si>
+    <t>0.9806,0.0095,0.0033,0.0045</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9976,0.0112</t>
+  </si>
+  <si>
+    <t>0.0125,0.0048,0.9767,0.0014</t>
+  </si>
+  <si>
+    <t>0.7634,0.0134,0.1265,0.0553</t>
+  </si>
+  <si>
+    <t>0.0109,0.0039,0.9762,0.0046</t>
+  </si>
+  <si>
+    <t>0.0050,0.9869,0.0137,0.0029</t>
+  </si>
+  <si>
+    <t>0.0020,0.9931,0.0302,0.0005</t>
+  </si>
+  <si>
+    <t>0.0338,0.9557,0.0152,0.0065</t>
+  </si>
+  <si>
+    <t>0.0279,0.9575,0.0177,0.0029</t>
+  </si>
+  <si>
+    <t>0.0087,0.9766,0.0408,0.0019</t>
+  </si>
+  <si>
+    <t>0.0043,0.9874,0.0107,0.0062</t>
+  </si>
+  <si>
+    <t>0.3813,0.6506,0.0258,0.0020</t>
+  </si>
+  <si>
+    <t>0.2135,0.4488,0.4081,0.0606</t>
+  </si>
+  <si>
+    <t>0.0281,0.0097,0.9616,0.0068</t>
+  </si>
+  <si>
+    <t>0.5195,0.1958,0.2666,0.0420</t>
+  </si>
+  <si>
+    <t>0.3853,0.0415,0.6354,0.0115</t>
+  </si>
+  <si>
+    <t>0.3158,0.1548,0.1968,0.4414</t>
+  </si>
+  <si>
+    <t>0.0001,0.9985,0.0124,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9971,0.0036,0.0030</t>
+  </si>
+  <si>
+    <t>0.0019,0.9927,0.0020,0.0098</t>
+  </si>
+  <si>
+    <t>0.0001,0.9957,0.6533,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.9789,0.0468,0.0003</t>
+  </si>
+  <si>
+    <t>0.8455,0.2030,0.0231,0.0015</t>
+  </si>
+  <si>
+    <t>0.7421,0.2336,0.0775,0.0027</t>
+  </si>
+  <si>
+    <t>0.9559,0.0226,0.0267,0.0034</t>
+  </si>
+  <si>
+    <t>0.9902,0.0042,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.9209,0.0637,0.0144,0.0105</t>
+  </si>
+  <si>
+    <t>0.9760,0.0116,0.0052,0.0059</t>
+  </si>
+  <si>
+    <t>0.9892,0.0046,0.0016,0.0021</t>
+  </si>
+  <si>
+    <t>0.9653,0.0161,0.0219,0.0009</t>
+  </si>
+  <si>
+    <t>0.9777,0.0162,0.0044,0.0030</t>
+  </si>
+  <si>
+    <t>0.9798,0.0075,0.0013,0.0053</t>
+  </si>
+  <si>
+    <t>0.0144,0.3466,0.8503,0.0070</t>
+  </si>
+  <si>
+    <t>0.0132,0.2503,0.8660,0.0102</t>
+  </si>
+  <si>
+    <t>0.0050,0.1565,0.9119,0.0025</t>
+  </si>
+  <si>
+    <t>0.0197,0.0212,0.9546,0.0063</t>
+  </si>
+  <si>
+    <t>0.6027,0.0706,0.1309,0.1834</t>
+  </si>
+  <si>
+    <t>0.6806,0.0277,0.3592,0.0053</t>
+  </si>
+  <si>
+    <t>0.0939,0.0113,0.9238,0.0043</t>
+  </si>
+  <si>
+    <t>0.7808,0.0540,0.1399,0.0098</t>
+  </si>
+  <si>
+    <t>0.0524,0.0016,0.0018,0.9841</t>
+  </si>
+  <si>
+    <t>0.0019,0.0008,0.0020,0.9983</t>
+  </si>
+  <si>
+    <t>0.0031,0.0038,0.0018,0.9972</t>
+  </si>
+  <si>
+    <t>0.0088,0.0009,0.0032,0.9947</t>
+  </si>
+  <si>
+    <t>0.0005,0.8996,0.4952,0.0033</t>
+  </si>
+  <si>
+    <t>0.9567,0.0218,0.0221,0.0052</t>
+  </si>
+  <si>
+    <t>0.5687,0.2595,0.0827,0.0029</t>
+  </si>
+  <si>
+    <t>0.9831,0.0075,0.0053,0.0024</t>
+  </si>
+  <si>
+    <t>0.2342,0.7657,0.0305,0.0062</t>
+  </si>
+  <si>
+    <t>0.9766,0.0073,0.0030,0.0070</t>
+  </si>
+  <si>
+    <t>0.8765,0.0334,0.0686,0.0262</t>
+  </si>
+  <si>
+    <t>0.9776,0.0150,0.0075,0.0028</t>
+  </si>
+  <si>
+    <t>0.0011,0.1345,0.9743,0.0159</t>
+  </si>
+  <si>
+    <t>0.7125,0.0073,0.0056,0.3580</t>
+  </si>
+  <si>
+    <t>0.9187,0.0477,0.0122,0.0139</t>
+  </si>
+  <si>
+    <t>0.4362,0.5582,0.0681,0.0259</t>
+  </si>
+  <si>
+    <t>0.9110,0.0334,0.0554,0.0088</t>
+  </si>
+  <si>
+    <t>0.9140,0.0340,0.0521,0.0019</t>
+  </si>
+  <si>
+    <t>0.6265,0.2149,0.1006,0.0664</t>
+  </si>
+  <si>
+    <t>0.8348,0.0934,0.0573,0.0041</t>
+  </si>
+  <si>
+    <t>0.8627,0.0605,0.0789,0.0045</t>
+  </si>
+  <si>
+    <t>0.9236,0.0495,0.0221,0.0216</t>
+  </si>
+  <si>
+    <t>0.9843,0.0114,0.0046,0.0020</t>
+  </si>
+  <si>
+    <t>0.9787,0.0129,0.0104,0.0017</t>
+  </si>
+  <si>
+    <t>0.9780,0.0091,0.0041,0.0067</t>
+  </si>
+  <si>
+    <t>0.9793,0.0085,0.0083,0.0039</t>
+  </si>
+  <si>
+    <t>0.9762,0.0196,0.0081,0.0014</t>
+  </si>
+  <si>
+    <t>0.9821,0.0055,0.0059,0.0039</t>
+  </si>
+  <si>
+    <t>0.9826,0.0119,0.0026,0.0018</t>
+  </si>
+  <si>
+    <t>0.3980,0.5891,0.0719,0.0072</t>
+  </si>
+  <si>
+    <t>0.1242,0.8428,0.0460,0.0030</t>
+  </si>
+  <si>
+    <t>0.2608,0.8240,0.0103,0.0037</t>
+  </si>
+  <si>
+    <t>0.0109,0.2358,0.9808,0.0007</t>
+  </si>
+  <si>
+    <t>0.9369,0.0758,0.0107,0.0059</t>
+  </si>
+  <si>
+    <t>0.9444,0.0584,0.0127,0.0045</t>
+  </si>
+  <si>
+    <t>0.9598,0.0319,0.0199,0.0020</t>
+  </si>
+  <si>
+    <t>0.9173,0.0811,0.0269,0.0058</t>
+  </si>
+  <si>
+    <t>0.0001,0.0171,0.9992,0.0004</t>
+  </si>
+  <si>
+    <t>0.9364,0.0266,0.0511,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.0020,0.9893,0.0082</t>
+  </si>
+  <si>
+    <t>0.0014,0.0011,0.9885,0.0094</t>
+  </si>
+  <si>
+    <t>0.0092,0.0018,0.9781,0.0036</t>
+  </si>
+  <si>
+    <t>0.0001,0.0078,0.9979,0.0031</t>
+  </si>
+  <si>
+    <t>0.0019,0.0023,0.9886,0.0033</t>
+  </si>
+  <si>
+    <t>0.0016,0.0015,0.9857,0.0120</t>
+  </si>
+  <si>
+    <t>0.0005,0.0024,0.9957,0.0032</t>
+  </si>
+  <si>
+    <t>0.1917,0.0226,0.8119,0.0035</t>
+  </si>
+  <si>
+    <t>0.0606,0.0112,0.9492,0.0021</t>
+  </si>
+  <si>
+    <t>0.5935,0.1593,0.2863,0.0175</t>
+  </si>
+  <si>
+    <t>0.1528,0.6148,0.2279,0.0137</t>
+  </si>
+  <si>
+    <t>0.2404,0.1245,0.5379,0.0049</t>
+  </si>
+  <si>
+    <t>0.7531,0.0146,0.3388,0.0034</t>
+  </si>
+  <si>
+    <t>0.6098,0.0464,0.3835,0.0135</t>
+  </si>
+  <si>
+    <t>0.1447,0.0691,0.8174,0.0094</t>
+  </si>
+  <si>
+    <t>0.5855,0.4691,0.0318,0.0024</t>
+  </si>
+  <si>
+    <t>0.3907,0.6009,0.0593,0.0044</t>
+  </si>
+  <si>
+    <t>0.4646,0.5574,0.0601,0.0042</t>
+  </si>
+  <si>
+    <t>0.7343,0.2783,0.0436,0.0032</t>
+  </si>
+  <si>
+    <t>0.6055,0.4453,0.0278,0.0042</t>
+  </si>
+  <si>
+    <t>0.8020,0.0218,0.2374,0.0034</t>
+  </si>
+  <si>
+    <t>0.9171,0.0062,0.1108,0.0026</t>
+  </si>
+  <si>
+    <t>0.6345,0.0543,0.1556,0.1252</t>
+  </si>
+  <si>
+    <t>0.5811,0.0274,0.5107,0.0085</t>
+  </si>
+  <si>
+    <t>0.6617,0.0173,0.2959,0.0390</t>
+  </si>
+  <si>
+    <t>0.0070,0.0034,0.9595,0.0295</t>
+  </si>
+  <si>
+    <t>0.0064,0.0213,0.9508,0.0386</t>
+  </si>
+  <si>
+    <t>0.0106,0.0261,0.9422,0.0331</t>
+  </si>
+  <si>
+    <t>0.0173,0.0220,0.9287,0.0212</t>
+  </si>
+  <si>
+    <t>0.0192,0.0671,0.8567,0.0348</t>
+  </si>
+  <si>
+    <t>0.9776,0.0162,0.0033,0.0042</t>
+  </si>
+  <si>
+    <t>0.9769,0.0249,0.0068,0.0009</t>
+  </si>
+  <si>
+    <t>0.9629,0.0319,0.0171,0.0023</t>
+  </si>
+  <si>
+    <t>0.9835,0.0175,0.0046,0.0010</t>
+  </si>
+  <si>
+    <t>0.9788,0.0185,0.0055,0.0022</t>
+  </si>
+  <si>
+    <t>0.9461,0.0334,0.0201,0.0115</t>
+  </si>
+  <si>
+    <t>0.9878,0.0087,0.0024,0.0015</t>
+  </si>
+  <si>
+    <t>0.9774,0.0126,0.0073,0.0040</t>
+  </si>
+  <si>
+    <t>0.1266,0.0475,0.8921,0.0089</t>
+  </si>
+  <si>
+    <t>0.1602,0.1139,0.7859,0.0037</t>
+  </si>
+  <si>
+    <t>0.8516,0.0357,0.1201,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.0018,0.9937,0.0063</t>
+  </si>
+  <si>
+    <t>0.0004,0.0137,0.9909,0.0066</t>
+  </si>
+  <si>
+    <t>0.0063,0.0206,0.9745,0.0034</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9977,0.0056</t>
+  </si>
+  <si>
+    <t>0.0035,0.0279,0.9455,0.0233</t>
+  </si>
+  <si>
+    <t>0.0000,0.0024,0.9986,0.0017</t>
+  </si>
+  <si>
+    <t>0.0015,0.0018,0.9856,0.0073</t>
+  </si>
+  <si>
+    <t>0.0275,0.0389,0.9199,0.0104</t>
+  </si>
+  <si>
+    <t>0.7424,0.0809,0.1697,0.0442</t>
+  </si>
+  <si>
+    <t>0.6396,0.0448,0.3454,0.0511</t>
+  </si>
+  <si>
+    <t>0.7149,0.0246,0.3669,0.0132</t>
+  </si>
+  <si>
+    <t>0.9618,0.0433,0.0121,0.0020</t>
+  </si>
+  <si>
+    <t>0.9813,0.0127,0.0062,0.0023</t>
+  </si>
+  <si>
+    <t>0.9882,0.0066,0.0034,0.0013</t>
+  </si>
+  <si>
+    <t>0.9749,0.0190,0.0054,0.0039</t>
+  </si>
+  <si>
+    <t>0.9801,0.0163,0.0041,0.0034</t>
+  </si>
+  <si>
+    <t>0.9762,0.0194,0.0086,0.0012</t>
+  </si>
+  <si>
+    <t>0.9487,0.0669,0.0142,0.0052</t>
+  </si>
+  <si>
+    <t>0.9745,0.0093,0.0128,0.0031</t>
+  </si>
+  <si>
+    <t>0.0025,0.0025,0.9895,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.0026,0.9964,0.0023</t>
+  </si>
+  <si>
+    <t>0.0004,0.0073,0.9897,0.0082</t>
+  </si>
+  <si>
+    <t>0.0492,0.0109,0.9291,0.0059</t>
+  </si>
+  <si>
+    <t>0.0069,0.0054,0.9792,0.0084</t>
+  </si>
+  <si>
+    <t>0.0248,0.0015,0.6308,0.3863</t>
+  </si>
+  <si>
+    <t>0.1653,0.0497,0.8241,0.0191</t>
+  </si>
+  <si>
+    <t>0.0832,0.0261,0.6405,0.2476</t>
+  </si>
+  <si>
+    <t>0.9149,0.0067,0.0118,0.0703</t>
+  </si>
+  <si>
+    <t>0.0193,0.0081,0.0170,0.9816</t>
+  </si>
+  <si>
+    <t>0.2511,0.0028,0.0028,0.9124</t>
+  </si>
+  <si>
+    <t>0.0346,0.0002,0.0007,0.9916</t>
+  </si>
+  <si>
+    <t>0.0085,0.0011,0.0040,0.9947</t>
+  </si>
+  <si>
+    <t>0.7443,0.0277,0.0270,0.1663</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3138,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3667,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4006,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4731,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
